--- a/Simulation/sim_results.xlsx
+++ b/Simulation/sim_results.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Mobina\Marquette\FAE Codes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Mobina\Marquette\FAE Codes\Simulation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79EA74C7-5BD1-45FA-AAF8-93E905FFACBB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DD1FCFB-BF44-4BA0-A539-EBCD7A34766F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9684" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -308,11 +308,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$C$1</c:f>
+              <c:f>Sheet1!$D$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>fpca_recon_relMSE_vs_clean</c:v>
+                  <c:v>fpca_recon_relMSE_vs_noisy</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -343,39 +343,39 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$C$2:$C$11</c:f>
+              <c:f>Sheet1!$D$2:$D$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>0.1171807795763016</c:v>
+                  <c:v>0.1178259402513504</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.1161510869860649</c:v>
+                  <c:v>0.1169094145298004</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.1149157285690308</c:v>
+                  <c:v>0.1156478449702263</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.11646696180105209</c:v>
+                  <c:v>0.1172283962368965</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.1144421920180321</c:v>
+                  <c:v>0.115203469991684</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.1129489839076996</c:v>
+                  <c:v>0.11369761079549789</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.11407105624675749</c:v>
+                  <c:v>0.1148358061909676</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.1151083558797836</c:v>
+                  <c:v>0.1158600077033043</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.1185520440340042</c:v>
+                  <c:v>0.1193290576338768</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.1178816184401512</c:v>
+                  <c:v>0.11862734705209731</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -392,11 +392,11 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$E$1</c:f>
+              <c:f>Sheet1!$F$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>fae_recon_relMSE_vs_clean</c:v>
+                  <c:v>fae_recon_relMSE_vs_noisy</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -427,39 +427,39 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$E$2:$E$11</c:f>
+              <c:f>Sheet1!$F$2:$F$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>3.158409520983696E-2</c:v>
+                  <c:v>3.2347377389669418E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3.3564105629920959E-2</c:v>
+                  <c:v>3.436780720949173E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.5469556450843811E-2</c:v>
+                  <c:v>2.6319954544305801E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.567918598651886E-2</c:v>
+                  <c:v>2.6538008823990818E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>8.5102669894695282E-2</c:v>
+                  <c:v>8.5759855806827545E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>7.6155297458171844E-2</c:v>
+                  <c:v>7.6979152858257294E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>5.2536472678184509E-2</c:v>
+                  <c:v>5.3366281092166901E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.066042065620422E-2</c:v>
+                  <c:v>3.1503282487392432E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.4514676779508591E-2</c:v>
+                  <c:v>3.5374142229557037E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>4.0906652808189392E-2</c:v>
+                  <c:v>4.1718963533639908E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -753,11 +753,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$I$1</c:f>
+              <c:f>Sheet1!$J$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>fpca_fore_relMSE_vs_clean</c:v>
+                  <c:v>fpca_fore_relMSE_vs_noisy</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -788,39 +788,39 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$I$2:$I$11</c:f>
+              <c:f>Sheet1!$J$2:$J$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>0.31091812252998352</c:v>
+                  <c:v>0.30953887104988098</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.25734764337539667</c:v>
+                  <c:v>0.26156789064407349</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.3447546660900116</c:v>
+                  <c:v>0.34946280717849731</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.31378838419914251</c:v>
+                  <c:v>0.31843486428260798</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.35720768570899958</c:v>
+                  <c:v>0.36208018660545349</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.35838437080383301</c:v>
+                  <c:v>0.36319929361343378</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.35227534174919128</c:v>
+                  <c:v>0.35715433955192571</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.30571910738945007</c:v>
+                  <c:v>0.31029814481735229</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.33608931303024292</c:v>
+                  <c:v>0.3406718373298645</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.3493974506855011</c:v>
+                  <c:v>0.35426220297813421</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -837,11 +837,11 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$K$1</c:f>
+              <c:f>Sheet1!$L$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>fae_fore_relMSE_vs_clean</c:v>
+                  <c:v>fae_fore_relMSE_vs_noisy</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -872,39 +872,39 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$K$2:$K$11</c:f>
+              <c:f>Sheet1!$L$2:$L$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>0.20507299900054929</c:v>
+                  <c:v>0.20698726177215579</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.15267570316791529</c:v>
+                  <c:v>0.15612752735614779</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.21326328814029691</c:v>
+                  <c:v>0.21722245216369629</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.19132603704929349</c:v>
+                  <c:v>0.19531804323196411</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.22714200615882871</c:v>
+                  <c:v>0.23124136030673981</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.23626916110515589</c:v>
+                  <c:v>0.24072021245956421</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.22071002423763281</c:v>
+                  <c:v>0.22505734860897059</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.18419185280799871</c:v>
+                  <c:v>0.1880994588136673</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.1999839246273041</c:v>
+                  <c:v>0.20350104570388791</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.2265363484621048</c:v>
+                  <c:v>0.23095965385437009</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2588,13 +2588,13 @@
       <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
@@ -2606,13 +2606,13 @@
       <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="5" t="s">
         <v>11</v>
       </c>
       <c r="M1" s="1" t="s">
@@ -3334,17 +3334,33 @@
         <f>AVERAGE(C2:C11)</f>
         <v>0.11577188074588776</v>
       </c>
+      <c r="D13" s="7">
+        <f>AVERAGE(D2:D11)</f>
+        <v>0.11651648953557014</v>
+      </c>
       <c r="E13" s="6">
         <f>AVERAGE(E2:E11)</f>
         <v>4.3617313355207445E-2</v>
       </c>
+      <c r="F13" s="6">
+        <f>AVERAGE(F2:F11)</f>
+        <v>4.4427482597529891E-2</v>
+      </c>
       <c r="I13" s="7">
         <f>AVERAGE(I2:I11)</f>
         <v>0.32858820855617521</v>
       </c>
+      <c r="J13" s="7">
+        <f>AVERAGE(J2:J11)</f>
+        <v>0.33266704380512235</v>
+      </c>
       <c r="K13" s="6">
         <f>AVERAGE(K2:K11)</f>
         <v>0.205717134475708</v>
+      </c>
+      <c r="L13" s="6">
+        <f>AVERAGE(L2:L11)</f>
+        <v>0.20952343642711641</v>
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.3">
@@ -3355,17 +3371,33 @@
         <f>1-C13</f>
         <v>0.88422811925411227</v>
       </c>
+      <c r="D14" s="7">
+        <f>1-D13</f>
+        <v>0.88348351046442986</v>
+      </c>
       <c r="E14" s="6">
         <f>1-E13</f>
         <v>0.95638268664479253</v>
       </c>
+      <c r="F14" s="6">
+        <f>1-F13</f>
+        <v>0.95557251740247007</v>
+      </c>
       <c r="I14" s="7">
         <f>1-I13</f>
         <v>0.67141179144382479</v>
       </c>
+      <c r="J14" s="7">
+        <f>1-J13</f>
+        <v>0.66733295619487765</v>
+      </c>
       <c r="K14" s="6">
         <f>1-K13</f>
         <v>0.79428286552429195</v>
+      </c>
+      <c r="L14" s="6">
+        <f>1-L13</f>
+        <v>0.79047656357288365</v>
       </c>
     </row>
   </sheetData>
